--- a/Assignment-2.XLSX
+++ b/Assignment-2.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91994\Desktop\assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5901534A-782A-4237-88FD-63035AAE2FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E25DD9-1CD1-4276-B30C-03D9EFC53CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E948E46A-B42D-40F5-893F-67A707190ABD}"/>
   </bookViews>
@@ -457,7 +457,221 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FB32F3ED-92A0-4ACB-8214-8407FB712906}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="33">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -486,71 +700,6 @@
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -565,20 +714,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6A732DF-DB1F-4DD7-90E9-51B810C79A7C}" name="Table3" displayName="Table3" ref="A1:I32" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6A732DF-DB1F-4DD7-90E9-51B810C79A7C}" name="Table3" displayName="Table3" ref="A1:I32" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
   <autoFilter ref="A1:I32" xr:uid="{C6A732DF-DB1F-4DD7-90E9-51B810C79A7C}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{32526939-FD29-40BF-BE4E-C28ECC1F3A7B}" name="Product ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{95CD6DDD-3DBF-4417-9894-F2EF07C1FAC6}" name="Manufacturing Date" dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{D4974DDE-E2AD-434C-97BF-3BD74D83589C}" name="counry code" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{065F60D7-199D-4A14-AB5E-7547BF33F15B}" name="Product Name" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{D81C9513-D586-4CD3-BE0F-C09FE7BF8AAD}" name="Brand Name" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{31861905-820D-48F4-93B8-74551C2EEDAD}" name="Product Brand" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{32526939-FD29-40BF-BE4E-C28ECC1F3A7B}" name="Product ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{95CD6DDD-3DBF-4417-9894-F2EF07C1FAC6}" name="Manufacturing Date" dataDxfId="29" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{D4974DDE-E2AD-434C-97BF-3BD74D83589C}" name="counry code" dataDxfId="28" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{065F60D7-199D-4A14-AB5E-7547BF33F15B}" name="Product Name" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{D81C9513-D586-4CD3-BE0F-C09FE7BF8AAD}" name="Brand Name" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{31861905-820D-48F4-93B8-74551C2EEDAD}" name="Product Brand" dataDxfId="25">
       <calculatedColumnFormula>D2&amp;"-"&amp;E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{514A8BF3-B29F-4825-8A83-193DED6AAF9C}" name="Price ($)" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{4B1CE60D-2FD8-437C-BD32-2D0B977EC135}" name="Quantity" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{471FDE0C-4C5D-46E8-A75A-DD3528FDFE77}" name="Category" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{514A8BF3-B29F-4825-8A83-193DED6AAF9C}" name="Price ($)" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{4B1CE60D-2FD8-437C-BD32-2D0B977EC135}" name="Quantity" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{471FDE0C-4C5D-46E8-A75A-DD3528FDFE77}" name="Category" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1874,7 +2023,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:G6 G8:G1048576">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1888,7 +2037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1902,16 +2051,92 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Electronics">
+    <cfRule type="containsText" dxfId="21" priority="18" operator="containsText" text="Electronics">
       <formula>NOT(ISERROR(SEARCH("Electronics",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" text="Electronics">
+    <cfRule type="containsText" priority="19" operator="containsText" text="Electronics">
       <formula>NOT(ISERROR(SEARCH("Electronics",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:I32">
+    <cfRule type="expression" dxfId="19" priority="16">
+      <formula>$I$5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:I32">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>12="Electronics"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:I2">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>SUM($A$2:$I$2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:I5">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>SUM($A$5:$I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:I7">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>SUM($A$7:$I$7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:I10">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>SUM($A$10:$I$10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:I12">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>SUM($A$12:$I$12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:I15">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>SUM($A$15:$I$15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:I18">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>SUM($A$18:$I$18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:I16">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>SUM($A$16:$I$16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:I19">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>SUM($A$19:$I$19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:I22">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>SUM($A$22:$I$22)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:I24">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>SUM($A$24:$I$24)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:I25">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>SUM($A$25:$I$25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:I30">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>SUM($A$30:$I$30)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
